--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_maule.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_maule.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.20640544574481</v>
+      </c>
+      <c r="C2">
         <v>28.17726568929683</v>
-      </c>
-      <c r="C2">
-        <v>27.20640544574481</v>
       </c>
       <c r="D2">
         <v>3.548960396039604</v>
       </c>
       <c r="E2">
-        <v>18.1339940570772</v>
+        <v>17.5091792123383</v>
       </c>
       <c r="F2">
         <v>64.3568267305845</v>
       </c>
       <c r="G2">
-        <v>17.5091792123383</v>
+        <v>18.1339940570772</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>29.19185343625035</v>
+      </c>
+      <c r="C3">
         <v>24.71868315818841</v>
-      </c>
-      <c r="C3">
-        <v>29.19185343625035</v>
       </c>
       <c r="D3">
         <v>4.045522949586155</v>
       </c>
       <c r="E3">
-        <v>16.06042296072508</v>
+        <v>18.96676737160121</v>
       </c>
       <c r="F3">
         <v>64.97280966767372</v>
       </c>
       <c r="G3">
-        <v>18.96676737160121</v>
+        <v>16.06042296072508</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>25.16719464977121</v>
+      </c>
+      <c r="C4">
         <v>48.99683210137275</v>
-      </c>
-      <c r="C4">
-        <v>25.16719464977121</v>
       </c>
       <c r="D4">
         <v>2.040948275862069</v>
       </c>
       <c r="E4">
-        <v>28.13257881972514</v>
+        <v>14.45028294260307</v>
       </c>
       <c r="F4">
         <v>57.41713823767179</v>
       </c>
       <c r="G4">
-        <v>14.45028294260307</v>
+        <v>28.13257881972514</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>32.46865542585387</v>
+      </c>
+      <c r="C5">
         <v>32.33895373973195</v>
-      </c>
-      <c r="C5">
-        <v>32.46865542585387</v>
       </c>
       <c r="D5">
         <v>3.092245989304813</v>
       </c>
       <c r="E5">
-        <v>19.62224554039874</v>
+        <v>19.700944386149</v>
       </c>
       <c r="F5">
         <v>60.67681007345226</v>
       </c>
       <c r="G5">
-        <v>19.700944386149</v>
+        <v>19.62224554039874</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>37.24333174159219</v>
+      </c>
+      <c r="C6">
         <v>17.33065011255884</v>
-      </c>
-      <c r="C6">
-        <v>37.24333174159219</v>
       </c>
       <c r="D6">
         <v>5.770123991340287</v>
       </c>
       <c r="E6">
+        <v>24.09417891345602</v>
+      </c>
+      <c r="F6">
+        <v>64.69394059755507</v>
+      </c>
+      <c r="G6">
         <v>11.21188048898892</v>
-      </c>
-      <c r="F6">
-        <v>64.69394059755506</v>
-      </c>
-      <c r="G6">
-        <v>24.09417891345602</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>25.6398252184769</v>
+      </c>
+      <c r="C7">
         <v>34.0980024968789</v>
-      </c>
-      <c r="C7">
-        <v>25.6398252184769</v>
       </c>
       <c r="D7">
         <v>2.932723112128147</v>
       </c>
       <c r="E7">
+        <v>16.05119187182493</v>
+      </c>
+      <c r="F7">
+        <v>62.60257913247363</v>
+      </c>
+      <c r="G7">
         <v>21.34622899570144</v>
-      </c>
-      <c r="F7">
-        <v>62.60257913247361</v>
-      </c>
-      <c r="G7">
-        <v>16.05119187182493</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>20.52401746724891</v>
+      </c>
+      <c r="C8">
         <v>32.26923656075893</v>
-      </c>
-      <c r="C8">
-        <v>20.52401746724891</v>
       </c>
       <c r="D8">
         <v>3.098926738217452</v>
       </c>
       <c r="E8">
-        <v>21.11954272198679</v>
+        <v>13.43254163792254</v>
       </c>
       <c r="F8">
-        <v>65.44791564009066</v>
+        <v>65.44791564009067</v>
       </c>
       <c r="G8">
-        <v>13.43254163792254</v>
+        <v>21.1195427219868</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>28.38538792627746</v>
+      </c>
+      <c r="C9">
         <v>31.23275576647169</v>
-      </c>
-      <c r="C9">
-        <v>28.38538792627746</v>
       </c>
       <c r="D9">
         <v>3.201766784452297</v>
       </c>
       <c r="E9">
-        <v>19.56717140289014</v>
+        <v>17.78330913365139</v>
       </c>
       <c r="F9">
         <v>62.64951946345849</v>
       </c>
       <c r="G9">
-        <v>17.78330913365139</v>
+        <v>19.56717140289014</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.81683941502201</v>
+      </c>
+      <c r="C10">
         <v>29.86653414738038</v>
-      </c>
-      <c r="C10">
-        <v>29.81683941502201</v>
       </c>
       <c r="D10">
         <v>3.348229141906347</v>
       </c>
       <c r="E10">
-        <v>18.70359667452096</v>
+        <v>18.67247588138532</v>
       </c>
       <c r="F10">
         <v>62.62392744409372</v>
       </c>
       <c r="G10">
-        <v>18.67247588138532</v>
+        <v>18.70359667452096</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>27.18609143593046</v>
+      </c>
+      <c r="C11">
         <v>28.61558274307792</v>
-      </c>
-      <c r="C11">
-        <v>27.18609143593046</v>
       </c>
       <c r="D11">
         <v>3.494599459945995</v>
       </c>
       <c r="E11">
-        <v>18.36667217721938</v>
+        <v>17.44916515126467</v>
       </c>
       <c r="F11">
-        <v>64.18416267151596</v>
+        <v>64.18416267151595</v>
       </c>
       <c r="G11">
-        <v>17.44916515126468</v>
+        <v>18.36667217721937</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.14893617021276</v>
+      </c>
+      <c r="C12">
         <v>37.04740574841359</v>
-      </c>
-      <c r="C12">
-        <v>29.14893617021276</v>
       </c>
       <c r="D12">
         <v>2.699244332493703</v>
       </c>
       <c r="E12">
+        <v>17.53885544874674</v>
+      </c>
+      <c r="F12">
+        <v>60.16979606504357</v>
+      </c>
+      <c r="G12">
         <v>22.29134848620969</v>
-      </c>
-      <c r="F12">
-        <v>60.16979606504358</v>
-      </c>
-      <c r="G12">
-        <v>17.53885544874674</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>28.11478387213948</v>
+      </c>
+      <c r="C13">
         <v>36.75989829277152</v>
-      </c>
-      <c r="C13">
-        <v>28.11478387213948</v>
       </c>
       <c r="D13">
         <v>2.720355731225296</v>
       </c>
       <c r="E13">
-        <v>22.29565983696849</v>
+        <v>17.0522141440846</v>
       </c>
       <c r="F13">
-        <v>60.6521260189469</v>
+        <v>60.65212601894692</v>
       </c>
       <c r="G13">
-        <v>17.0522141440846</v>
+        <v>22.2956598369685</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>26.58178256611166</v>
+      </c>
+      <c r="C14">
         <v>38.57002938295788</v>
-      </c>
-      <c r="C14">
-        <v>26.58178256611166</v>
       </c>
       <c r="D14">
         <v>2.592686642965973</v>
       </c>
       <c r="E14">
-        <v>23.35428774759815</v>
+        <v>16.09536235322026</v>
       </c>
       <c r="F14">
         <v>60.55034989918158</v>
       </c>
       <c r="G14">
-        <v>16.09536235322026</v>
+        <v>23.35428774759815</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>27.40526429870607</v>
+      </c>
+      <c r="C15">
         <v>24.28494689523235</v>
-      </c>
-      <c r="C15">
-        <v>27.40526429870607</v>
       </c>
       <c r="D15">
         <v>4.117777174123948</v>
       </c>
       <c r="E15">
-        <v>16.0095675944334</v>
+        <v>18.06660039761432</v>
       </c>
       <c r="F15">
         <v>65.92383200795229</v>
       </c>
       <c r="G15">
-        <v>18.06660039761432</v>
+        <v>16.0095675944334</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>25.29474812433012</v>
+      </c>
+      <c r="C16">
         <v>38.66176695758689</v>
-      </c>
-      <c r="C16">
-        <v>25.29474812433012</v>
       </c>
       <c r="D16">
         <v>2.586534653465347</v>
       </c>
       <c r="E16">
-        <v>23.58050056032872</v>
+        <v>15.427717594322</v>
       </c>
       <c r="F16">
         <v>60.99178184534927</v>
       </c>
       <c r="G16">
-        <v>15.427717594322</v>
+        <v>23.58050056032872</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>26.77795563686256</v>
+      </c>
+      <c r="C17">
         <v>34.46146809970272</v>
-      </c>
-      <c r="C17">
-        <v>26.77795563686256</v>
       </c>
       <c r="D17">
         <v>2.901791639017917</v>
       </c>
       <c r="E17">
-        <v>21.37285491419657</v>
+        <v>16.60757339384485</v>
       </c>
       <c r="F17">
         <v>62.01957169195858</v>
       </c>
       <c r="G17">
-        <v>16.60757339384485</v>
+        <v>21.37285491419657</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>29.59323966332451</v>
+      </c>
+      <c r="C18">
         <v>29.44569263270849</v>
-      </c>
-      <c r="C18">
-        <v>29.59323966332451</v>
       </c>
       <c r="D18">
         <v>3.396082450745929</v>
       </c>
       <c r="E18">
-        <v>18.51477006768296</v>
+        <v>18.60754422586291</v>
       </c>
       <c r="F18">
         <v>62.87768570645412</v>
       </c>
       <c r="G18">
-        <v>18.60754422586291</v>
+        <v>18.51477006768296</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>30.04026014245896</v>
+      </c>
+      <c r="C19">
         <v>32.75007742335088</v>
-      </c>
-      <c r="C19">
-        <v>30.04026014245896</v>
       </c>
       <c r="D19">
         <v>3.053427895981088</v>
       </c>
       <c r="E19">
-        <v>20.11794920574527</v>
+        <v>18.45334347950157</v>
       </c>
       <c r="F19">
         <v>61.42870731475315</v>
       </c>
       <c r="G19">
-        <v>18.45334347950157</v>
+        <v>20.11794920574527</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>26.68904380755659</v>
+      </c>
+      <c r="C20">
         <v>26.67183062225665</v>
-      </c>
-      <c r="C20">
-        <v>26.68904380755659</v>
       </c>
       <c r="D20">
         <v>3.749273959341723</v>
       </c>
       <c r="E20">
-        <v>17.39154834726977</v>
+        <v>17.40277232167911</v>
       </c>
       <c r="F20">
         <v>65.20567933105113</v>
       </c>
       <c r="G20">
-        <v>17.40277232167911</v>
+        <v>17.39154834726977</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>25.22045855379189</v>
+      </c>
+      <c r="C21">
         <v>29.91822991822992</v>
-      </c>
-      <c r="C21">
-        <v>25.22045855379189</v>
       </c>
       <c r="D21">
         <v>3.342443729903537</v>
       </c>
       <c r="E21">
-        <v>19.28482844150476</v>
+        <v>16.25671765192228</v>
       </c>
       <c r="F21">
-        <v>64.45845390657297</v>
+        <v>64.45845390657296</v>
       </c>
       <c r="G21">
-        <v>16.25671765192228</v>
+        <v>19.28482844150475</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>27.01444368022856</v>
+      </c>
+      <c r="C22">
         <v>29.04079149251362</v>
-      </c>
-      <c r="C22">
-        <v>27.01444368022856</v>
       </c>
       <c r="D22">
         <v>3.443432319183822</v>
       </c>
       <c r="E22">
-        <v>18.60930295633306</v>
+        <v>17.31082180634662</v>
       </c>
       <c r="F22">
         <v>64.07987523732031</v>
       </c>
       <c r="G22">
-        <v>17.31082180634662</v>
+        <v>18.60930295633306</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>26.60079051383399</v>
+      </c>
+      <c r="C23">
         <v>39.1304347826087</v>
-      </c>
-      <c r="C23">
-        <v>26.60079051383399</v>
       </c>
       <c r="D23">
         <v>2.555555555555555</v>
       </c>
       <c r="E23">
-        <v>23.61077987121393</v>
+        <v>16.05056045790603</v>
       </c>
       <c r="F23">
         <v>60.33865967088004</v>
       </c>
       <c r="G23">
-        <v>16.05056045790603</v>
+        <v>23.61077987121393</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>27.9741971326718</v>
+      </c>
+      <c r="C24">
         <v>29.03594191268384</v>
-      </c>
-      <c r="C24">
-        <v>27.9741971326718</v>
       </c>
       <c r="D24">
         <v>3.444007440871645</v>
       </c>
       <c r="E24">
-        <v>18.49303623907766</v>
+        <v>17.81680934922991</v>
       </c>
       <c r="F24">
         <v>63.69015441169244</v>
       </c>
       <c r="G24">
-        <v>17.81680934922991</v>
+        <v>18.49303623907766</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>30.73602907769196</v>
+      </c>
+      <c r="C25">
         <v>31.78858094805391</v>
-      </c>
-      <c r="C25">
-        <v>30.73602907769196</v>
       </c>
       <c r="D25">
         <v>3.145783706526918</v>
       </c>
       <c r="E25">
-        <v>19.55924148534687</v>
+        <v>18.91161533802357</v>
       </c>
       <c r="F25">
         <v>61.52914317662955</v>
       </c>
       <c r="G25">
-        <v>18.91161533802357</v>
+        <v>19.55924148534687</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>27.47426761678543</v>
+      </c>
+      <c r="C26">
         <v>31.21140142517815</v>
-      </c>
-      <c r="C26">
-        <v>27.47426761678543</v>
       </c>
       <c r="D26">
         <v>3.203957382039574</v>
       </c>
       <c r="E26">
-        <v>19.66869573894821</v>
+        <v>17.31364135315837</v>
       </c>
       <c r="F26">
         <v>63.01766290789343</v>
       </c>
       <c r="G26">
-        <v>17.31364135315837</v>
+        <v>19.66869573894821</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>29.59245974204381</v>
+      </c>
+      <c r="C27">
         <v>33.39693200030528</v>
-      </c>
-      <c r="C27">
-        <v>29.59245974204381</v>
       </c>
       <c r="D27">
         <v>2.994287020109689</v>
       </c>
       <c r="E27">
-        <v>20.49024887036734</v>
+        <v>18.15606489827453</v>
       </c>
       <c r="F27">
         <v>61.35368623135813</v>
       </c>
       <c r="G27">
-        <v>18.15606489827453</v>
+        <v>20.49024887036734</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>29.10118899143593</v>
+      </c>
+      <c r="C28">
         <v>33.29176020620271</v>
-      </c>
-      <c r="C28">
-        <v>29.10118899143593</v>
       </c>
       <c r="D28">
         <v>3.003746253746254</v>
       </c>
       <c r="E28">
-        <v>20.50074240950284</v>
+        <v>17.92022937893605</v>
       </c>
       <c r="F28">
         <v>61.57902821156111</v>
       </c>
       <c r="G28">
-        <v>17.92022937893605</v>
+        <v>20.50074240950284</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>28.58394554155153</v>
+      </c>
+      <c r="C29">
         <v>30.21837298645278</v>
-      </c>
-      <c r="C29">
-        <v>28.58394554155153</v>
       </c>
       <c r="D29">
         <v>3.309245009479202</v>
       </c>
       <c r="E29">
-        <v>19.02892430447977</v>
+        <v>17.99970290516309</v>
       </c>
       <c r="F29">
         <v>62.97137279035716</v>
       </c>
       <c r="G29">
-        <v>17.99970290516309</v>
+        <v>19.02892430447977</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>28.45520187124987</v>
+      </c>
+      <c r="C30">
         <v>35.44187938574188</v>
-      </c>
-      <c r="C30">
-        <v>28.45520187124987</v>
       </c>
       <c r="D30">
         <v>2.821520803443328</v>
       </c>
       <c r="E30">
-        <v>21.62447257383966</v>
+        <v>17.36162819558203</v>
       </c>
       <c r="F30">
         <v>61.01389923057831</v>
       </c>
       <c r="G30">
-        <v>17.36162819558203</v>
+        <v>21.62447257383966</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>31.60877513711152</v>
+      </c>
+      <c r="C31">
         <v>30.03656307129799</v>
-      </c>
-      <c r="C31">
-        <v>31.60877513711152</v>
       </c>
       <c r="D31">
         <v>3.329275715155204</v>
       </c>
       <c r="E31">
-        <v>18.58176883058132</v>
+        <v>19.5543994571364</v>
       </c>
       <c r="F31">
         <v>61.86383171228229</v>
       </c>
       <c r="G31">
-        <v>19.5543994571364</v>
+        <v>18.58176883058132</v>
       </c>
     </row>
   </sheetData>
